--- a/salidas/empresas/SBUX.xlsx
+++ b/salidas/empresas/SBUX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>11.6258430480957</v>
+        <v>11.62584209442139</v>
       </c>
       <c r="C2" t="n">
         <v>15.85000038146973</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.3202075958252</v>
+        <v>13.32021045684814</v>
       </c>
       <c r="C3" t="n">
         <v>18.15999984741211</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.80064105987549</v>
+        <v>13.8006477355957</v>
       </c>
       <c r="C4" t="n">
         <v>18.81500053405762</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>13.66862106323242</v>
+        <v>13.66861343383789</v>
       </c>
       <c r="C5" t="n">
         <v>18.63500022888184</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.84832096099854</v>
+        <v>13.84832000732422</v>
       </c>
       <c r="C7" t="n">
         <v>18.8799991607666</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>12.55371379852295</v>
+        <v>12.55370903015137</v>
       </c>
       <c r="C8" t="n">
         <v>17.11499977111816</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>12.48769760131836</v>
+        <v>12.48769378662109</v>
       </c>
       <c r="C10" t="n">
         <v>17.02499961853027</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>13.84465789794922</v>
+        <v>13.8446569442749</v>
       </c>
       <c r="C11" t="n">
         <v>18.875</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>12.94246101379395</v>
+        <v>12.94246482849121</v>
       </c>
       <c r="C12" t="n">
         <v>17.64500045776367</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.99013710021973</v>
+        <v>12.99013519287109</v>
       </c>
       <c r="C13" t="n">
         <v>17.70999908447266</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.8140983581543</v>
+        <v>12.81409549713135</v>
       </c>
       <c r="C14" t="n">
         <v>17.46999931335449</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.33244228363037</v>
+        <v>11.332444190979</v>
       </c>
       <c r="C15" t="n">
         <v>15.44999980926514</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.50115299224854</v>
+        <v>11.5011510848999</v>
       </c>
       <c r="C16" t="n">
         <v>15.68000030517578</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>11.37645626068115</v>
+        <v>11.37645530700684</v>
       </c>
       <c r="C17" t="n">
         <v>15.51000022888184</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>10.56594753265381</v>
+        <v>10.56594657897949</v>
       </c>
       <c r="C18" t="n">
         <v>14.40499973297119</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>9.623410224914551</v>
+        <v>9.623412132263184</v>
       </c>
       <c r="C19" t="n">
         <v>13.11999988555908</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>9.78477954864502</v>
+        <v>9.784778594970703</v>
       </c>
       <c r="C20" t="n">
         <v>13.34000015258789</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>10.10384750366211</v>
+        <v>10.10385036468506</v>
       </c>
       <c r="C21" t="n">
         <v>13.77499961853027</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>9.608739852905273</v>
+        <v>9.608738899230957</v>
       </c>
       <c r="C22" t="n">
         <v>13.10000038146973</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>9.78477954864502</v>
+        <v>9.784778594970703</v>
       </c>
       <c r="C23" t="n">
         <v>13.34000015258789</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>8.578187942504883</v>
+        <v>8.578184127807617</v>
       </c>
       <c r="C24" t="n">
         <v>11.69499969482422</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>7.507287502288818</v>
+        <v>7.507291793823242</v>
       </c>
       <c r="C25" t="n">
         <v>10.23499965667725</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>6.935164451599121</v>
+        <v>6.935163021087646</v>
       </c>
       <c r="C26" t="n">
         <v>9.454999923706055</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>6.418050765991211</v>
+        <v>6.418054103851318</v>
       </c>
       <c r="C28" t="n">
         <v>8.75</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>5.952284336090088</v>
+        <v>5.952283382415771</v>
       </c>
       <c r="C29" t="n">
         <v>8.114999771118164</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>6.671108245849609</v>
+        <v>6.671105861663818</v>
       </c>
       <c r="C30" t="n">
         <v>9.095000267028809</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.772580146789551</v>
+        <v>5.772578239440918</v>
       </c>
       <c r="C31" t="n">
         <v>7.869999885559082</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>5.70656681060791</v>
+        <v>5.706565856933594</v>
       </c>
       <c r="C33" t="n">
         <v>7.78000020980835</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>5.453510284423828</v>
+        <v>5.453511238098145</v>
       </c>
       <c r="C34" t="n">
         <v>7.434999942779541</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>3.275039911270142</v>
+        <v>3.275040149688721</v>
       </c>
       <c r="C36" t="n">
         <v>4.465000152587891</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>3.469415426254272</v>
+        <v>3.469416618347168</v>
       </c>
       <c r="C37" t="n">
         <v>4.730000019073486</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>3.462080240249634</v>
+        <v>3.462080001831055</v>
       </c>
       <c r="C38" t="n">
         <v>4.71999979019165</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>3.355724096298218</v>
+        <v>3.355725288391113</v>
       </c>
       <c r="C39" t="n">
         <v>4.574999809265137</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>5.303143501281738</v>
+        <v>5.303144454956055</v>
       </c>
       <c r="C41" t="n">
         <v>7.230000019073486</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>5.277472972869873</v>
+        <v>5.277472496032715</v>
       </c>
       <c r="C42" t="n">
         <v>7.195000171661377</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>5.094101428985596</v>
+        <v>5.094100475311279</v>
       </c>
       <c r="C43" t="n">
         <v>6.945000171661377</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>6.491402626037598</v>
+        <v>6.491402149200439</v>
       </c>
       <c r="C44" t="n">
         <v>8.850000381469727</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>6.964504718780518</v>
+        <v>6.964502334594727</v>
       </c>
       <c r="C45" t="n">
         <v>9.494999885559082</v>
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>6.960837364196777</v>
+        <v>6.960834980010986</v>
       </c>
       <c r="C47" t="n">
         <v>9.489999771118164</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>8.031735420227051</v>
+        <v>8.031733512878418</v>
       </c>
       <c r="C48" t="n">
         <v>10.94999980926514</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>8.457159042358398</v>
+        <v>8.457161903381348</v>
       </c>
       <c r="C49" t="n">
         <v>11.52999973297119</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.991392135620117</v>
+        <v>7.991390705108643</v>
       </c>
       <c r="C50" t="n">
         <v>10.89500045776367</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.402144432067871</v>
+        <v>8.402145385742188</v>
       </c>
       <c r="C51" t="n">
         <v>11.45499992370605</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>8.900921821594238</v>
+        <v>8.900922775268555</v>
       </c>
       <c r="C52" t="n">
         <v>12.13500022888184</v>
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>9.534382820129395</v>
+        <v>9.534385681152344</v>
       </c>
       <c r="C54" t="n">
         <v>12.94499969482422</v>
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>9.151382446289062</v>
+        <v>9.151388168334961</v>
       </c>
       <c r="C56" t="n">
         <v>12.42500019073486</v>
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>10.57296180725098</v>
+        <v>10.57296085357666</v>
       </c>
       <c r="C59" t="n">
         <v>14.27999973297119</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>11.37620830535889</v>
+        <v>11.3762035369873</v>
       </c>
       <c r="C60" t="n">
         <v>15.30000019073486</v>
@@ -1703,11 +1715,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>11.94501781463623</v>
+        <v>11.94501686096191</v>
       </c>
       <c r="C61" t="n">
         <v>16.06500053405762</v>
@@ -1732,11 +1744,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>11.72195434570312</v>
+        <v>11.72195243835449</v>
       </c>
       <c r="C62" t="n">
         <v>15.76500034332275</v>
@@ -1761,11 +1773,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.31014251708984</v>
+        <v>12.31014156341553</v>
       </c>
       <c r="C63" t="n">
         <v>16.48999977111816</v>
@@ -1790,11 +1802,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>13.79198360443115</v>
+        <v>13.79198551177979</v>
       </c>
       <c r="C64" t="n">
         <v>18.47500038146973</v>
@@ -1819,11 +1831,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.51204586029053</v>
+        <v>13.51204013824463</v>
       </c>
       <c r="C65" t="n">
         <v>18.10000038146973</v>
@@ -1848,11 +1860,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.78131198883057</v>
+        <v>13.78130626678467</v>
       </c>
       <c r="C66" t="n">
         <v>18.39500045776367</v>
@@ -1877,11 +1889,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>14.79271125793457</v>
+        <v>14.79271221160889</v>
       </c>
       <c r="C67" t="n">
         <v>19.7450008392334</v>
@@ -1906,11 +1918,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>15.0174674987793</v>
+        <v>15.01746368408203</v>
       </c>
       <c r="C68" t="n">
         <v>20.04500007629395</v>
@@ -1935,11 +1947,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>14.51821422576904</v>
+        <v>14.51821231842041</v>
       </c>
       <c r="C69" t="n">
         <v>19.30999946594238</v>
@@ -1964,11 +1976,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>14.01823329925537</v>
+        <v>14.0182409286499</v>
       </c>
       <c r="C70" t="n">
         <v>18.64500045776367</v>
@@ -1993,11 +2005,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>15.92417526245117</v>
+        <v>15.92417812347412</v>
       </c>
       <c r="C71" t="n">
         <v>21.18000030517578</v>
@@ -2022,11 +2034,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>16.40913391113281</v>
+        <v>16.40913200378418</v>
       </c>
       <c r="C72" t="n">
         <v>21.73999977111816</v>
@@ -2051,11 +2063,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>17.36394119262695</v>
+        <v>17.36393356323242</v>
       </c>
       <c r="C73" t="n">
         <v>23.0049991607666</v>
@@ -2080,11 +2092,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>18.08476829528809</v>
+        <v>18.08476638793945</v>
       </c>
       <c r="C74" t="n">
         <v>23.95999908447266</v>
@@ -2109,7 +2121,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2138,11 +2150,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>21.16707420349121</v>
+        <v>21.16706848144531</v>
       </c>
       <c r="C76" t="n">
         <v>27.94499969482422</v>
@@ -2167,11 +2179,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>21.72758102416992</v>
+        <v>21.72758483886719</v>
       </c>
       <c r="C77" t="n">
         <v>28.68499946594238</v>
@@ -2196,11 +2208,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>20.85214614868164</v>
+        <v>20.85214996337891</v>
       </c>
       <c r="C78" t="n">
         <v>27.44499969482422</v>
@@ -2225,11 +2237,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>20.2557201385498</v>
+        <v>20.25572204589844</v>
       </c>
       <c r="C79" t="n">
         <v>26.65999984741211</v>
@@ -2254,11 +2266,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>17.20140838623047</v>
+        <v>17.20140266418457</v>
       </c>
       <c r="C80" t="n">
         <v>22.63999938964844</v>
@@ -2283,11 +2295,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>18.91957664489746</v>
+        <v>18.91957855224609</v>
       </c>
       <c r="C81" t="n">
         <v>24.80500030517578</v>
@@ -2312,11 +2324,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>19.33908081054688</v>
+        <v>19.33908271789551</v>
       </c>
       <c r="C82" t="n">
         <v>25.35499954223633</v>
@@ -2341,7 +2353,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2370,11 +2382,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>19.86377143859863</v>
+        <v>19.86376571655273</v>
       </c>
       <c r="C84" t="n">
         <v>25.93499946594238</v>
@@ -2399,11 +2411,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>20.53777313232422</v>
+        <v>20.53776931762695</v>
       </c>
       <c r="C85" t="n">
         <v>26.81500053405762</v>
@@ -2428,7 +2440,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2457,11 +2469,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>21.08390998840332</v>
+        <v>21.08391380310059</v>
       </c>
       <c r="C87" t="n">
         <v>27.42499923706055</v>
@@ -2486,11 +2498,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>21.89113616943359</v>
+        <v>21.89112854003906</v>
       </c>
       <c r="C88" t="n">
         <v>28.47500038146973</v>
@@ -2515,11 +2527,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>23.38641738891602</v>
+        <v>23.38642501831055</v>
       </c>
       <c r="C89" t="n">
         <v>30.42000007629395</v>
@@ -2544,11 +2556,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>24.35236930847168</v>
+        <v>24.35237312316895</v>
       </c>
       <c r="C90" t="n">
         <v>31.56999969482422</v>
@@ -2573,11 +2585,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.26645278930664</v>
+        <v>25.26645660400391</v>
       </c>
       <c r="C91" t="n">
         <v>32.75500106811523</v>
@@ -2602,11 +2614,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>27.49573707580566</v>
+        <v>27.49574089050293</v>
       </c>
       <c r="C92" t="n">
         <v>35.64500045776367</v>
@@ -2631,7 +2643,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2660,11 +2672,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>29.77096748352051</v>
+        <v>29.77096366882324</v>
       </c>
       <c r="C94" t="n">
         <v>38.48500061035156</v>
@@ -2689,11 +2701,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>31.34906387329102</v>
+        <v>31.34906005859375</v>
       </c>
       <c r="C95" t="n">
         <v>40.52500152587891</v>
@@ -2718,7 +2730,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2747,11 +2759,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>30.41784858703613</v>
+        <v>30.4178466796875</v>
       </c>
       <c r="C97" t="n">
         <v>39.19499969482422</v>
@@ -2776,11 +2788,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>27.59685897827148</v>
+        <v>27.59684944152832</v>
       </c>
       <c r="C98" t="n">
         <v>35.56000137329102</v>
@@ -2805,11 +2817,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>27.63896560668945</v>
+        <v>27.63895988464355</v>
       </c>
       <c r="C99" t="n">
         <v>35.47999954223633</v>
@@ -2834,11 +2846,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>28.58155059814453</v>
+        <v>28.5815486907959</v>
       </c>
       <c r="C100" t="n">
         <v>36.68999862670898</v>
@@ -2863,11 +2875,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>27.50654411315918</v>
+        <v>27.50653266906738</v>
       </c>
       <c r="C101" t="n">
         <v>35.31000137329102</v>
@@ -2892,11 +2904,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>28.63199424743652</v>
+        <v>28.63199043273926</v>
       </c>
       <c r="C102" t="n">
         <v>36.61999893188477</v>
@@ -2921,11 +2933,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>30.25046157836914</v>
+        <v>30.25045204162598</v>
       </c>
       <c r="C103" t="n">
         <v>38.68999862670898</v>
@@ -2950,11 +2962,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>30.36774826049805</v>
+        <v>30.36772537231445</v>
       </c>
       <c r="C104" t="n">
         <v>38.84000015258789</v>
@@ -2979,11 +2991,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>30.52091598510742</v>
+        <v>30.52090263366699</v>
       </c>
       <c r="C105" t="n">
         <v>38.90499877929688</v>
@@ -3008,11 +3020,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>29.59912109375</v>
+        <v>29.59913444519043</v>
       </c>
       <c r="C106" t="n">
         <v>37.72999954223633</v>
@@ -3037,11 +3049,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>29.63835525512695</v>
+        <v>29.63834381103516</v>
       </c>
       <c r="C107" t="n">
         <v>37.77999877929688</v>
@@ -3066,11 +3078,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>31.98614883422852</v>
+        <v>31.98614120483398</v>
       </c>
       <c r="C108" t="n">
         <v>40.60499954223633</v>
@@ -3095,11 +3107,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>32.31698608398438</v>
+        <v>32.31697845458984</v>
       </c>
       <c r="C109" t="n">
         <v>41.02500152587891</v>
@@ -3124,11 +3136,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>34.47538757324219</v>
+        <v>34.47538375854492</v>
       </c>
       <c r="C110" t="n">
         <v>43.76499938964844</v>
@@ -3153,11 +3165,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>36.9572639465332</v>
+        <v>36.95725631713867</v>
       </c>
       <c r="C111" t="n">
         <v>46.74499893188477</v>
@@ -3182,11 +3194,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>37.43558883666992</v>
+        <v>37.43558120727539</v>
       </c>
       <c r="C112" t="n">
         <v>47.34999847412109</v>
@@ -3211,11 +3223,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>39.19863891601562</v>
+        <v>39.19865798950195</v>
       </c>
       <c r="C113" t="n">
         <v>49.58000183105469</v>
@@ -3240,11 +3252,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>41.21101760864258</v>
+        <v>41.21101379394531</v>
       </c>
       <c r="C114" t="n">
         <v>51.95999908447266</v>
@@ -3269,11 +3281,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>42.52761077880859</v>
+        <v>42.52760696411133</v>
       </c>
       <c r="C115" t="n">
         <v>53.61999893188477</v>
@@ -3298,11 +3310,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>45.94599914550781</v>
+        <v>45.94599151611328</v>
       </c>
       <c r="C116" t="n">
         <v>57.93000030517578</v>
@@ -3327,11 +3339,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>43.51176071166992</v>
+        <v>43.51175308227539</v>
       </c>
       <c r="C117" t="n">
         <v>54.70999908447266</v>
@@ -3356,11 +3368,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>45.20577239990234</v>
+        <v>45.20578765869141</v>
       </c>
       <c r="C118" t="n">
         <v>56.84000015258789</v>
@@ -3385,11 +3397,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>49.7629508972168</v>
+        <v>49.76294326782227</v>
       </c>
       <c r="C119" t="n">
         <v>62.56999969482422</v>
@@ -3414,7 +3426,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3443,7 +3455,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3472,11 +3484,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>48.48786926269531</v>
+        <v>48.48785400390625</v>
       </c>
       <c r="C122" t="n">
         <v>60.77000045776367</v>
@@ -3501,11 +3513,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>46.59704971313477</v>
+        <v>46.59704208374023</v>
       </c>
       <c r="C123" t="n">
         <v>58.20999908447266</v>
@@ -3530,7 +3542,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3559,7 +3571,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3588,11 +3600,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>44.09312438964844</v>
+        <v>44.0931282043457</v>
       </c>
       <c r="C126" t="n">
         <v>54.88999938964844</v>
@@ -3617,11 +3629,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>45.88447189331055</v>
+        <v>45.88448333740234</v>
       </c>
       <c r="C127" t="n">
         <v>57.11999893188477</v>
@@ -3646,11 +3658,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>46.63156127929688</v>
+        <v>46.63155746459961</v>
       </c>
       <c r="C128" t="n">
         <v>58.04999923706055</v>
@@ -3675,11 +3687,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>45.32685852050781</v>
+        <v>45.32684707641602</v>
       </c>
       <c r="C129" t="n">
         <v>56.22999954223633</v>
@@ -3704,11 +3716,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>43.6421012878418</v>
+        <v>43.64210891723633</v>
       </c>
       <c r="C130" t="n">
         <v>54.13999938964844</v>
@@ -3733,11 +3745,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>42.77958297729492</v>
+        <v>42.77957534790039</v>
       </c>
       <c r="C131" t="n">
         <v>53.06999969482422</v>
@@ -3762,11 +3774,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>46.94592666625977</v>
+        <v>46.9459228515625</v>
       </c>
       <c r="C132" t="n">
         <v>57.97000122070312</v>
@@ -3791,11 +3803,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>44.96183013916016</v>
+        <v>44.96183395385742</v>
       </c>
       <c r="C133" t="n">
         <v>55.52000045776367</v>
@@ -3820,11 +3832,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>44.71888732910156</v>
+        <v>44.71887969970703</v>
       </c>
       <c r="C134" t="n">
         <v>55.22000122070312</v>
@@ -3849,11 +3861,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>46.26263046264648</v>
+        <v>46.26263427734375</v>
       </c>
       <c r="C135" t="n">
         <v>56.86999893188477</v>
@@ -3878,11 +3890,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>47.49913024902344</v>
+        <v>47.49912643432617</v>
       </c>
       <c r="C136" t="n">
         <v>58.38999938964844</v>
@@ -3907,11 +3919,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>48.85765075683594</v>
+        <v>48.85763931274414</v>
       </c>
       <c r="C137" t="n">
         <v>60.06000137329102</v>
@@ -3936,11 +3948,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>51.95865631103516</v>
+        <v>51.95864868164062</v>
       </c>
       <c r="C138" t="n">
         <v>63.61000061035156</v>
@@ -3965,11 +3977,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>47.62944412231445</v>
+        <v>47.62943649291992</v>
       </c>
       <c r="C139" t="n">
         <v>58.31000137329102</v>
@@ -3994,11 +4006,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>44.09256362915039</v>
+        <v>44.09257125854492</v>
       </c>
       <c r="C140" t="n">
         <v>53.97999954223633</v>
@@ -4023,11 +4035,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>45.01366424560547</v>
+        <v>45.0136604309082</v>
       </c>
       <c r="C141" t="n">
         <v>54.86000061035156</v>
@@ -4052,7 +4064,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4081,11 +4093,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>44.99724960327148</v>
+        <v>44.99724578857422</v>
       </c>
       <c r="C143" t="n">
         <v>54.84000015258789</v>
@@ -4110,11 +4122,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>47.69373321533203</v>
+        <v>47.6937370300293</v>
       </c>
       <c r="C144" t="n">
         <v>57.81999969482422</v>
@@ -4139,7 +4151,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4168,11 +4180,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>46.86061096191406</v>
+        <v>46.86061859130859</v>
       </c>
       <c r="C146" t="n">
         <v>56.81000137329102</v>
@@ -4197,11 +4209,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>47.35528564453125</v>
+        <v>47.35529708862305</v>
       </c>
       <c r="C147" t="n">
         <v>57.09999847412109</v>
@@ -4226,11 +4238,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>48.01047515869141</v>
+        <v>48.01047897338867</v>
       </c>
       <c r="C148" t="n">
         <v>57.88999938964844</v>
@@ -4255,11 +4267,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>47.74508285522461</v>
+        <v>47.74508666992188</v>
       </c>
       <c r="C149" t="n">
         <v>57.56999969482422</v>
@@ -4284,11 +4296,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>47.24444198608398</v>
+        <v>47.24443817138672</v>
       </c>
       <c r="C150" t="n">
         <v>56.66999816894531</v>
@@ -4313,11 +4325,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>40.72508239746094</v>
+        <v>40.72509384155273</v>
       </c>
       <c r="C151" t="n">
         <v>48.84999847412109</v>
@@ -4342,11 +4354,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>43.67631149291992</v>
+        <v>43.67631912231445</v>
       </c>
       <c r="C152" t="n">
         <v>52.38999938964844</v>
@@ -4371,11 +4383,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>44.8702278137207</v>
+        <v>44.87023162841797</v>
       </c>
       <c r="C153" t="n">
         <v>53.45000076293945</v>
@@ -4400,11 +4412,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>47.71606063842773</v>
+        <v>47.716064453125</v>
       </c>
       <c r="C154" t="n">
         <v>56.84000015258789</v>
@@ -4429,11 +4441,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>48.91652297973633</v>
+        <v>48.91653442382812</v>
       </c>
       <c r="C155" t="n">
         <v>58.27000045776367</v>
@@ -4458,11 +4470,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>56.31086730957031</v>
+        <v>56.31085586547852</v>
       </c>
       <c r="C156" t="n">
         <v>66.72000122070312</v>
@@ -4487,11 +4499,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>54.35281372070312</v>
+        <v>54.35280990600586</v>
       </c>
       <c r="C157" t="n">
         <v>64.40000152587891</v>
@@ -4516,11 +4528,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>57.50933456420898</v>
+        <v>57.50932312011719</v>
       </c>
       <c r="C158" t="n">
         <v>68.13999938964844</v>
@@ -4545,7 +4557,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4574,11 +4586,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>63.06949615478516</v>
+        <v>63.06948852539062</v>
       </c>
       <c r="C160" t="n">
         <v>74.33999633789062</v>
@@ -4603,11 +4615,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>65.90312957763672</v>
+        <v>65.90312194824219</v>
       </c>
       <c r="C161" t="n">
         <v>77.68000030517578</v>
@@ -4632,7 +4644,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4661,7 +4673,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4690,11 +4702,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>80.70696258544922</v>
+        <v>80.70695495605469</v>
       </c>
       <c r="C164" t="n">
         <v>94.69000244140625</v>
@@ -4719,11 +4731,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>82.61273956298828</v>
+        <v>82.61275482177734</v>
       </c>
       <c r="C165" t="n">
         <v>96.55999755859375</v>
@@ -4748,11 +4760,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>75.64851379394531</v>
+        <v>75.64850616455078</v>
       </c>
       <c r="C166" t="n">
         <v>88.41999816894531</v>
@@ -4777,11 +4789,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>72.34603118896484</v>
+        <v>72.34605407714844</v>
       </c>
       <c r="C167" t="n">
         <v>84.55999755859375</v>
@@ -4806,7 +4818,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4835,11 +4847,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>75.59674072265625</v>
+        <v>75.59671783447266</v>
       </c>
       <c r="C169" t="n">
         <v>87.91999816894531</v>
@@ -4864,11 +4876,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>72.93983459472656</v>
+        <v>72.93985748291016</v>
       </c>
       <c r="C170" t="n">
         <v>84.83000183105469</v>
@@ -4893,11 +4905,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>67.75119781494141</v>
+        <v>67.75119018554688</v>
       </c>
       <c r="C171" t="n">
         <v>78.43000030517578</v>
@@ -4922,11 +4934,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>56.78903961181641</v>
+        <v>56.78902816772461</v>
       </c>
       <c r="C172" t="n">
         <v>65.73999786376953</v>
@@ -4951,11 +4963,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>66.28266906738281</v>
+        <v>66.28265380859375</v>
       </c>
       <c r="C173" t="n">
         <v>76.73000335693359</v>
@@ -4980,11 +4992,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>67.75184631347656</v>
+        <v>67.75182342529297</v>
       </c>
       <c r="C174" t="n">
         <v>77.98999786376953</v>
@@ -5009,11 +5021,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>63.92945098876953</v>
+        <v>63.9294548034668</v>
       </c>
       <c r="C175" t="n">
         <v>73.58999633789062</v>
@@ -5038,11 +5050,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>66.48348999023438</v>
+        <v>66.48350524902344</v>
       </c>
       <c r="C176" t="n">
         <v>76.52999877929688</v>
@@ -5067,11 +5079,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>73.78033447265625</v>
+        <v>73.78034973144531</v>
       </c>
       <c r="C177" t="n">
         <v>84.47000122070312</v>
@@ -5096,11 +5108,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>75.046875</v>
+        <v>75.04685974121094</v>
       </c>
       <c r="C178" t="n">
         <v>85.91999816894531</v>
@@ -5125,11 +5137,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>75.95523071289062</v>
+        <v>75.95524597167969</v>
       </c>
       <c r="C179" t="n">
         <v>86.95999908447266</v>
@@ -5154,7 +5166,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5183,11 +5195,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>93.88236999511719</v>
+        <v>93.88236236572266</v>
       </c>
       <c r="C181" t="n">
         <v>106.9800033569336</v>
@@ -5212,11 +5224,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>84.95747375488281</v>
+        <v>84.95746612548828</v>
       </c>
       <c r="C182" t="n">
         <v>96.80999755859375</v>
@@ -5241,11 +5253,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>95.20741271972656</v>
+        <v>95.20742034912109</v>
       </c>
       <c r="C183" t="n">
         <v>108.0299987792969</v>
@@ -5270,7 +5282,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5299,11 +5311,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>100.9006423950195</v>
+        <v>100.900634765625</v>
       </c>
       <c r="C185" t="n">
         <v>114.4899978637695</v>
@@ -5328,11 +5340,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>100.7623519897461</v>
+        <v>100.7623596191406</v>
       </c>
       <c r="C186" t="n">
         <v>113.879997253418</v>
@@ -5357,11 +5369,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>98.9307861328125</v>
+        <v>98.93080139160156</v>
       </c>
       <c r="C187" t="n">
         <v>111.8099975585938</v>
@@ -5386,11 +5398,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>107.4426956176758</v>
+        <v>107.4427032470703</v>
       </c>
       <c r="C188" t="n">
         <v>121.4300003051758</v>
@@ -5415,7 +5427,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5444,7 +5456,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5473,11 +5485,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>94.21625518798828</v>
+        <v>94.21624755859375</v>
       </c>
       <c r="C191" t="n">
         <v>106.0699996948242</v>
@@ -5502,11 +5514,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>97.80720520019531</v>
+        <v>97.80721282958984</v>
       </c>
       <c r="C192" t="n">
         <v>109.6399993896484</v>
@@ -5531,11 +5543,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>104.3461303710938</v>
+        <v>104.3461227416992</v>
       </c>
       <c r="C193" t="n">
         <v>116.9700012207031</v>
@@ -5560,11 +5572,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>87.70890808105469</v>
+        <v>87.70890045166016</v>
       </c>
       <c r="C194" t="n">
         <v>98.31999969482422</v>
@@ -5589,11 +5601,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>82.298828125</v>
+        <v>82.29883575439453</v>
       </c>
       <c r="C195" t="n">
         <v>91.79000091552734</v>
@@ -5618,11 +5630,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>81.56361389160156</v>
+        <v>81.56362152099609</v>
       </c>
       <c r="C196" t="n">
         <v>90.97000122070312</v>
@@ -5647,11 +5659,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>66.92215728759766</v>
+        <v>66.92216491699219</v>
       </c>
       <c r="C197" t="n">
         <v>74.63999938964844</v>
@@ -5676,11 +5688,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>70.87876892089844</v>
+        <v>70.87875366210938</v>
       </c>
       <c r="C198" t="n">
         <v>78.5</v>
@@ -5705,11 +5717,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>68.97360229492188</v>
+        <v>68.97361755371094</v>
       </c>
       <c r="C199" t="n">
         <v>76.38999938964844</v>
@@ -5734,11 +5746,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>76.54904937744141</v>
+        <v>76.54905700683594</v>
       </c>
       <c r="C200" t="n">
         <v>84.77999877929688</v>
@@ -5763,11 +5775,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>76.34049224853516</v>
+        <v>76.34048461914062</v>
       </c>
       <c r="C201" t="n">
         <v>84.06999969482422</v>
@@ -5792,11 +5804,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>76.51302337646484</v>
+        <v>76.51300811767578</v>
       </c>
       <c r="C202" t="n">
         <v>84.26000213623047</v>
@@ -5821,11 +5833,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>78.62879943847656</v>
+        <v>78.62880706787109</v>
       </c>
       <c r="C203" t="n">
         <v>86.58999633789062</v>
@@ -5850,11 +5862,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>93.33695983886719</v>
+        <v>93.33694458007812</v>
       </c>
       <c r="C204" t="n">
         <v>102.1999969482422</v>
@@ -5879,11 +5891,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>90.59712219238281</v>
+        <v>90.59709930419922</v>
       </c>
       <c r="C205" t="n">
         <v>99.19999694824219</v>
@@ -5908,11 +5920,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>99.67507934570312</v>
+        <v>99.67507171630859</v>
       </c>
       <c r="C206" t="n">
         <v>109.1399993896484</v>
@@ -5937,7 +5949,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5966,7 +5978,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5995,11 +6007,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>104.9014892578125</v>
+        <v>104.901496887207</v>
       </c>
       <c r="C209" t="n">
         <v>114.2900009155273</v>
@@ -6024,7 +6036,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6053,7 +6065,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6082,11 +6094,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>93.69061279296875</v>
+        <v>93.69059753417969</v>
       </c>
       <c r="C212" t="n">
         <v>101.5699996948242</v>
@@ -6111,7 +6123,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6140,11 +6152,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>84.63856506347656</v>
+        <v>84.63857269287109</v>
       </c>
       <c r="C214" t="n">
         <v>91.26999664306641</v>
@@ -6169,7 +6181,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6198,7 +6210,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6227,11 +6239,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>89.5234375</v>
+        <v>89.52342987060547</v>
       </c>
       <c r="C217" t="n">
         <v>96.01000213623047</v>
@@ -6256,11 +6268,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>86.74474334716797</v>
+        <v>86.74476623535156</v>
       </c>
       <c r="C218" t="n">
         <v>93.02999877929688</v>
@@ -6285,11 +6297,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>89.02082061767578</v>
+        <v>89.02080535888672</v>
       </c>
       <c r="C219" t="n">
         <v>94.90000152587891</v>
@@ -6314,11 +6326,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>85.72824859619141</v>
+        <v>85.72826385498047</v>
       </c>
       <c r="C220" t="n">
         <v>91.38999938964844</v>
@@ -6343,11 +6355,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>83.00790405273438</v>
+        <v>83.00791168212891</v>
       </c>
       <c r="C221" t="n">
         <v>88.48999786376953</v>
@@ -6372,11 +6384,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>75.82117462158203</v>
+        <v>75.8211669921875</v>
       </c>
       <c r="C222" t="n">
         <v>80.22000122070312</v>
@@ -6401,11 +6413,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>73.58112335205078</v>
+        <v>73.58113098144531</v>
       </c>
       <c r="C223" t="n">
         <v>77.84999847412109</v>
@@ -6430,11 +6442,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>73.67563629150391</v>
+        <v>73.67564392089844</v>
       </c>
       <c r="C224" t="n">
         <v>77.94999694824219</v>
@@ -6459,11 +6471,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>89.92453002929688</v>
+        <v>89.92452239990234</v>
       </c>
       <c r="C225" t="n">
         <v>94.56999969482422</v>
@@ -6488,7 +6500,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6517,11 +6529,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>92.90076446533203</v>
+        <v>92.90077209472656</v>
       </c>
       <c r="C227" t="n">
         <v>97.69999694824219</v>
@@ -6546,11 +6558,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>98.02957153320312</v>
+        <v>98.02957916259766</v>
       </c>
       <c r="C228" t="n">
         <v>102.4599990844727</v>
@@ -6575,11 +6587,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>87.30429840087891</v>
+        <v>87.30429077148438</v>
       </c>
       <c r="C229" t="n">
         <v>91.25</v>
@@ -6604,11 +6616,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>103.0238571166992</v>
+        <v>103.0238647460938</v>
       </c>
       <c r="C230" t="n">
         <v>107.6800003051758</v>
@@ -6633,11 +6645,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>111.403678894043</v>
+        <v>111.4036865234375</v>
       </c>
       <c r="C231" t="n">
         <v>115.8099975585938</v>
@@ -6662,11 +6674,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>94.35790252685547</v>
+        <v>94.35788726806641</v>
       </c>
       <c r="C232" t="n">
         <v>98.08999633789062</v>
@@ -6691,11 +6703,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>77.0042724609375</v>
+        <v>77.00428009033203</v>
       </c>
       <c r="C233" t="n">
         <v>80.05000305175781</v>
@@ -6720,7 +6732,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6749,11 +6761,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>88.76420593261719</v>
+        <v>88.76419830322266</v>
       </c>
       <c r="C235" t="n">
         <v>91.62999725341797</v>
@@ -6778,11 +6790,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>86.37144470214844</v>
+        <v>86.3714599609375</v>
       </c>
       <c r="C236" t="n">
         <v>89.16000366210938</v>
@@ -6807,7 +6819,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6836,7 +6848,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6865,7 +6877,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6894,7 +6906,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6923,7 +6935,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6952,11 +6964,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>90.30966949462891</v>
+        <v>90.30966186523438</v>
       </c>
       <c r="C242" t="n">
         <v>91.94999694824219</v>
@@ -6981,11 +6993,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>96.89223480224609</v>
+        <v>96.89222717285156</v>
       </c>
       <c r="C243" t="n">
         <v>98.01999664306641</v>
@@ -7010,7 +7022,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7039,7 +7051,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7068,7 +7080,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7097,7 +7109,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7126,7 +7138,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7155,7 +7167,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7184,32 +7196,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>94.13999938964844</v>
+        <v>93.65000152587891</v>
       </c>
       <c r="C250" t="n">
-        <v>94.13999938964844</v>
+        <v>93.65000152587891</v>
       </c>
       <c r="D250" t="n">
-        <v>108755600</v>
+        <v>115986100</v>
       </c>
       <c r="E250" t="n">
         <v>1.73</v>
       </c>
       <c r="F250" t="n">
-        <v>54.4161846182939</v>
+        <v>54.13294885888954</v>
       </c>
       <c r="G250" t="n">
         <v>1140000000</v>
       </c>
       <c r="H250" t="n">
-        <v>107319599304.1992</v>
+        <v>106761001739.502</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09539964912280702</v>
+        <v>0.1017421929824561</v>
       </c>
     </row>
   </sheetData>
@@ -7241,75 +7253,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39628</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7345,13 +7357,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39720</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39810</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40211</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7387,13 +7399,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39811</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39901</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7429,13 +7441,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39902</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39992</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7471,13 +7483,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40084</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40174</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40211</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7513,13 +7525,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40175</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40265</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7555,13 +7567,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40266</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40356</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7597,13 +7609,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40357</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40454</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40504</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7630,7 +7642,7 @@
       <c r="I9" t="n">
         <v>0.62</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40504</v>
       </c>
       <c r="K9" t="n">
@@ -7643,13 +7655,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40455</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40545</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7676,7 +7688,7 @@
       <c r="I10" t="n">
         <v>0.6849999999999999</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="K10" t="n">
@@ -7689,13 +7701,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40546</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40636</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7722,7 +7734,7 @@
       <c r="I11" t="n">
         <v>0.715</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K11" t="n">
@@ -7735,13 +7747,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40637</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40727</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7768,7 +7780,7 @@
       <c r="I12" t="n">
         <v>0.76</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K12" t="n">
@@ -7781,13 +7793,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40728</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40818</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40865</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7814,7 +7826,7 @@
       <c r="I13" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40865</v>
       </c>
       <c r="K13" t="n">
@@ -7827,13 +7839,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40819</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7860,7 +7872,7 @@
       <c r="I14" t="n">
         <v>0.8350000000000002</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="K14" t="n">
@@ -7873,13 +7885,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40910</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7906,7 +7918,7 @@
       <c r="I15" t="n">
         <v>0.8650000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="K15" t="n">
@@ -7919,13 +7931,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41001</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7952,7 +7964,7 @@
       <c r="I16" t="n">
         <v>0.9</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K16" t="n">
@@ -7965,13 +7977,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41092</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41229</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7998,7 +8010,7 @@
       <c r="I17" t="n">
         <v>0.895</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41229</v>
       </c>
       <c r="K17" t="n">
@@ -8011,13 +8023,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41273</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41303</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8044,7 +8056,7 @@
       <c r="I18" t="n">
         <v>0.93</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41303</v>
       </c>
       <c r="K18" t="n">
@@ -8057,13 +8069,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8090,7 +8102,7 @@
       <c r="I19" t="n">
         <v>0.985</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="K19" t="n">
@@ -8103,13 +8115,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41366</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41485</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8136,7 +8148,7 @@
       <c r="I20" t="n">
         <v>1.045</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41485</v>
       </c>
       <c r="K20" t="n">
@@ -8149,13 +8161,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41596</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8182,7 +8194,7 @@
       <c r="I21" t="n">
         <v>0.005000000000000004</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41596</v>
       </c>
       <c r="K21" t="n">
@@ -8195,13 +8207,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41637</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41667</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8228,7 +8240,7 @@
       <c r="I22" t="n">
         <v>0.07499999999999996</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41667</v>
       </c>
       <c r="K22" t="n">
@@ -8241,13 +8253,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41638</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8274,7 +8286,7 @@
       <c r="I23" t="n">
         <v>0.09999999999999998</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="K23" t="n">
@@ -8287,13 +8299,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8320,7 +8332,7 @@
       <c r="I24" t="n">
         <v>0.16</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="K24" t="n">
@@ -8333,13 +8345,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41957</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8366,7 +8378,7 @@
       <c r="I25" t="n">
         <v>1.355</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41957</v>
       </c>
       <c r="K25" t="n">
@@ -8379,13 +8391,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41911</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42001</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42031</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8412,7 +8424,7 @@
       <c r="I26" t="n">
         <v>1.65</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42031</v>
       </c>
       <c r="K26" t="n">
@@ -8425,13 +8437,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42002</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8458,7 +8470,7 @@
       <c r="I27" t="n">
         <v>1.7</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="K27" t="n">
@@ -8471,13 +8483,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42093</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8504,7 +8516,7 @@
       <c r="I28" t="n">
         <v>1.775</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="K28" t="n">
@@ -8517,13 +8529,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42184</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42274</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42320</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8550,7 +8562,7 @@
       <c r="I29" t="n">
         <v>1.82</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42320</v>
       </c>
       <c r="K29" t="n">
@@ -8563,13 +8575,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42275</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42365</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42395</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8596,7 +8608,7 @@
       <c r="I30" t="n">
         <v>1.63</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42395</v>
       </c>
       <c r="K30" t="n">
@@ -8609,13 +8621,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42366</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42456</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8642,7 +8654,7 @@
       <c r="I31" t="n">
         <v>1.69</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="K31" t="n">
@@ -8655,13 +8667,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42457</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42547</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8688,7 +8700,7 @@
       <c r="I32" t="n">
         <v>1.79</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K32" t="n">
@@ -8701,13 +8713,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42548</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42645</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8734,7 +8746,7 @@
       <c r="I33" t="n">
         <v>1.9</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="K33" t="n">
@@ -8747,13 +8759,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42646</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8780,7 +8792,7 @@
       <c r="I34" t="n">
         <v>1.95</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="K34" t="n">
@@ -8793,13 +8805,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42737</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8826,7 +8838,7 @@
       <c r="I35" t="n">
         <v>2.01</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="K35" t="n">
@@ -8839,13 +8851,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42828</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8872,7 +8884,7 @@
       <c r="I36" t="n">
         <v>1.97</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="K36" t="n">
@@ -8885,13 +8897,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42919</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43056</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8918,7 +8930,7 @@
       <c r="I37" t="n">
         <v>1.97</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43056</v>
       </c>
       <c r="K37" t="n">
@@ -8931,13 +8943,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43010</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8964,7 +8976,7 @@
       <c r="I38" t="n">
         <v>3.03</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="K38" t="n">
@@ -8977,13 +8989,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9010,7 +9022,7 @@
       <c r="I39" t="n">
         <v>3.05</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="K39" t="n">
@@ -9023,13 +9035,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43192</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9056,7 +9068,7 @@
       <c r="I40" t="n">
         <v>3.19</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="K40" t="n">
@@ -9069,13 +9081,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43283</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43420</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9102,7 +9114,7 @@
       <c r="I41" t="n">
         <v>3.21</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43420</v>
       </c>
       <c r="K41" t="n">
@@ -9115,13 +9127,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43464</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43494</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9148,7 +9160,7 @@
       <c r="I42" t="n">
         <v>2.25</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43494</v>
       </c>
       <c r="K42" t="n">
@@ -9161,13 +9173,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9194,7 +9206,7 @@
       <c r="I43" t="n">
         <v>2.31</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K43" t="n">
@@ -9207,13 +9219,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9240,7 +9252,7 @@
       <c r="I44" t="n">
         <v>2.82</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="K44" t="n">
@@ -9253,13 +9265,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43784</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9286,7 +9298,7 @@
       <c r="I45" t="n">
         <v>2.93</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43784</v>
       </c>
       <c r="K45" t="n">
@@ -9299,13 +9311,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43828</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43858</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9332,7 +9344,7 @@
       <c r="I46" t="n">
         <v>3.06</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43858</v>
       </c>
       <c r="K46" t="n">
@@ -9345,13 +9357,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43829</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9378,7 +9390,7 @@
       <c r="I47" t="n">
         <v>2.81</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="K47" t="n">
@@ -9391,13 +9403,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43920</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9424,7 +9436,7 @@
       <c r="I48" t="n">
         <v>1.11</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="K48" t="n">
@@ -9437,13 +9449,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44011</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44101</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44147</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9470,7 +9482,7 @@
       <c r="I49" t="n">
         <v>0.77</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44147</v>
       </c>
       <c r="K49" t="n">
@@ -9483,13 +9495,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44102</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44192</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44222</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9516,7 +9528,7 @@
       <c r="I50" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44222</v>
       </c>
       <c r="K50" t="n">
@@ -9529,13 +9541,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44193</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44283</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9562,7 +9574,7 @@
       <c r="I51" t="n">
         <v>0.8400000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K51" t="n">
@@ -9575,13 +9587,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44284</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44374</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9608,7 +9620,7 @@
       <c r="I52" t="n">
         <v>2.39</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="K52" t="n">
@@ -9621,13 +9633,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44375</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44472</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9654,7 +9666,7 @@
       <c r="I53" t="n">
         <v>3.54</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="K53" t="n">
@@ -9667,13 +9679,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44473</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44563</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9700,7 +9712,7 @@
       <c r="I54" t="n">
         <v>3.7</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="K54" t="n">
@@ -9713,13 +9725,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44654</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9746,7 +9758,7 @@
       <c r="I55" t="n">
         <v>3.72</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K55" t="n">
@@ -9759,13 +9771,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44655</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44745</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9792,7 +9804,7 @@
       <c r="I56" t="n">
         <v>3.54</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K56" t="n">
@@ -9805,13 +9817,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44746</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44836</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9838,7 +9850,7 @@
       <c r="I57" t="n">
         <v>2.83</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="K57" t="n">
@@ -9851,13 +9863,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44837</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9884,7 +9896,7 @@
       <c r="I58" t="n">
         <v>2.88</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="K58" t="n">
@@ -9897,13 +9909,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44928</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45018</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9930,7 +9942,7 @@
       <c r="I59" t="n">
         <v>3.09</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K59" t="n">
@@ -9943,13 +9955,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45019</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45109</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9976,7 +9988,7 @@
       <c r="I60" t="n">
         <v>3.29</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="K60" t="n">
@@ -9989,13 +10001,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10022,7 +10034,7 @@
       <c r="I61" t="n">
         <v>3.58</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="K61" t="n">
@@ -10035,13 +10047,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10068,7 +10080,7 @@
       <c r="I62" t="n">
         <v>3.74</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="K62" t="n">
@@ -10081,13 +10093,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10114,7 +10126,7 @@
       <c r="I63" t="n">
         <v>3.63</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K63" t="n">
@@ -10127,13 +10139,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10160,7 +10172,7 @@
       <c r="I64" t="n">
         <v>3.57</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="K64" t="n">
@@ -10173,13 +10185,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45616</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10206,7 +10218,7 @@
       <c r="I65" t="n">
         <v>3.31</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45616</v>
       </c>
       <c r="K65" t="n">
@@ -10219,13 +10231,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45655</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45685</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10252,7 +10264,7 @@
       <c r="I66" t="n">
         <v>3.1</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45685</v>
       </c>
       <c r="K66" t="n">
@@ -10265,13 +10277,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45656</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10298,7 +10310,7 @@
       <c r="I67" t="n">
         <v>2.76</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K67" t="n">
@@ -10311,13 +10323,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10344,7 +10356,7 @@
       <c r="I68" t="n">
         <v>2.32</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="K68" t="n">
@@ -10357,13 +10369,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10390,7 +10402,7 @@
       <c r="I69" t="n">
         <v>1.63</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="K69" t="n">
@@ -10403,13 +10415,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45929</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46019</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46050</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10436,7 +10448,7 @@
       <c r="I70" t="n">
         <v>1.2</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46050</v>
       </c>
       <c r="K70" t="n">
@@ -10449,13 +10461,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46020</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46110</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10482,7 +10494,7 @@
       <c r="I71" t="n">
         <v>1.31</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="K71" t="n">
@@ -10495,13 +10507,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46111</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46201</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10528,7 +10540,7 @@
       <c r="I72" t="n">
         <v>1.73</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="K72" t="n">
@@ -10565,52 +10577,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39992</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="C2" t="n">
@@ -10639,10 +10651,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40130</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40137</v>
       </c>
       <c r="C3" t="n">
@@ -10671,10 +10683,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40204</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40211</v>
       </c>
       <c r="C4" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40294</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="C5" t="n">
@@ -10735,10 +10747,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40385</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="C6" t="n">
@@ -10767,10 +10779,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40494</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40504</v>
       </c>
       <c r="C7" t="n">
@@ -10799,10 +10811,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40571</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="C8" t="n">
@@ -10831,10 +10843,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10863,10 +10875,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10895,10 +10907,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40858</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40865</v>
       </c>
       <c r="C11" t="n">
@@ -10927,10 +10939,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40933</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="C12" t="n">
@@ -10959,10 +10971,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41024</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="C13" t="n">
@@ -10991,10 +11003,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41115</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C14" t="n">
@@ -11023,10 +11035,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41222</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41229</v>
       </c>
       <c r="C15" t="n">
@@ -11055,10 +11067,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41297</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41303</v>
       </c>
       <c r="C16" t="n">
@@ -11087,10 +11099,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41388</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="C17" t="n">
@@ -11119,10 +11131,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41479</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41485</v>
       </c>
       <c r="C18" t="n">
@@ -11151,10 +11163,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41586</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41596</v>
       </c>
       <c r="C19" t="n">
@@ -11183,10 +11195,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41661</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41667</v>
       </c>
       <c r="C20" t="n">
@@ -11215,10 +11227,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41752</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="C21" t="n">
@@ -11247,10 +11259,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41843</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="C22" t="n">
@@ -11279,10 +11291,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41950</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41957</v>
       </c>
       <c r="C23" t="n">
@@ -11311,10 +11323,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42025</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42031</v>
       </c>
       <c r="C24" t="n">
@@ -11343,10 +11355,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42116</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="C25" t="n">
@@ -11375,10 +11387,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42207</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="C26" t="n">
@@ -11407,10 +11419,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42314</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42320</v>
       </c>
       <c r="C27" t="n">
@@ -11439,10 +11451,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42389</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42395</v>
       </c>
       <c r="C28" t="n">
@@ -11471,10 +11483,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42480</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="C29" t="n">
@@ -11503,10 +11515,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42571</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C30" t="n">
@@ -11535,10 +11547,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42685</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="C31" t="n">
@@ -11567,10 +11579,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42760</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="C32" t="n">
@@ -11599,10 +11611,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42851</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C33" t="n">
@@ -11631,10 +11643,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42943</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C34" t="n">
@@ -11663,10 +11675,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43049</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43056</v>
       </c>
       <c r="C35" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43124</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="C36" t="n">
@@ -11727,10 +11739,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43215</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C37" t="n">
@@ -11759,10 +11771,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43306</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="C38" t="n">
@@ -11791,10 +11803,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43413</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43420</v>
       </c>
       <c r="C39" t="n">
@@ -11823,10 +11835,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43488</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43494</v>
       </c>
       <c r="C40" t="n">
@@ -11855,10 +11867,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43579</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C41" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43670</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="C42" t="n">
@@ -11919,10 +11931,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43777</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43784</v>
       </c>
       <c r="C43" t="n">
@@ -11951,10 +11963,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43852</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43858</v>
       </c>
       <c r="C44" t="n">
@@ -11983,10 +11995,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43943</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="C45" t="n">
@@ -12015,10 +12027,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44034</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="C46" t="n">
@@ -12047,10 +12059,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44141</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44147</v>
       </c>
       <c r="C47" t="n">
@@ -12079,10 +12091,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44216</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44222</v>
       </c>
       <c r="C48" t="n">
@@ -12111,10 +12123,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44307</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C49" t="n">
@@ -12143,10 +12155,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44398</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="C50" t="n">
@@ -12175,10 +12187,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44512</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="C51" t="n">
@@ -12207,10 +12219,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44587</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="C52" t="n">
@@ -12239,10 +12251,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44678</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C53" t="n">
@@ -12271,10 +12283,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44769</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C54" t="n">
@@ -12303,10 +12315,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44876</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="C55" t="n">
@@ -12335,10 +12347,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44953</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="C56" t="n">
@@ -12367,10 +12379,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45042</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C57" t="n">
@@ -12399,10 +12411,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C58" t="n">
@@ -12431,10 +12443,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45240</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="C59" t="n">
@@ -12463,10 +12475,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45315</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="C60" t="n">
@@ -12495,10 +12507,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45406</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C61" t="n">
@@ -12527,10 +12539,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="C62" t="n">
@@ -12559,10 +12571,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45609</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45616</v>
       </c>
       <c r="C63" t="n">
@@ -12591,10 +12603,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45679</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45685</v>
       </c>
       <c r="C64" t="n">
@@ -12623,10 +12635,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45770</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C65" t="n">
@@ -12655,10 +12667,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45861</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="C66" t="n">
@@ -12687,10 +12699,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45968</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="C67" t="n">
@@ -12719,10 +12731,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46044</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46050</v>
       </c>
       <c r="C68" t="n">
@@ -12751,10 +12763,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="C69" t="n">
@@ -12783,10 +12795,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46226</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="C70" t="n">
@@ -12833,12 +12845,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/SBUX.xlsx
+++ b/salidas/empresas/SBUX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>11.62584209442139</v>
+        <v>11.62584400177002</v>
       </c>
       <c r="C2" t="n">
         <v>15.85000038146973</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.32021045684814</v>
+        <v>13.3202075958252</v>
       </c>
       <c r="C3" t="n">
         <v>18.15999984741211</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.8006477355957</v>
+        <v>13.80065059661865</v>
       </c>
       <c r="C4" t="n">
         <v>18.81500053405762</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>13.66861343383789</v>
+        <v>13.66861820220947</v>
       </c>
       <c r="C5" t="n">
         <v>18.63500022888184</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>13.07448768615723</v>
+        <v>13.07449340820312</v>
       </c>
       <c r="C6" t="n">
         <v>17.82500076293945</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.84832000732422</v>
+        <v>13.84832668304443</v>
       </c>
       <c r="C7" t="n">
         <v>18.8799991607666</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>12.55370903015137</v>
+        <v>12.5537109375</v>
       </c>
       <c r="C8" t="n">
         <v>17.11499977111816</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>11.3727912902832</v>
+        <v>11.37278842926025</v>
       </c>
       <c r="C9" t="n">
         <v>15.50500011444092</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>12.48769378662109</v>
+        <v>12.48769664764404</v>
       </c>
       <c r="C10" t="n">
         <v>17.02499961853027</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>13.8446569442749</v>
+        <v>13.84465885162354</v>
       </c>
       <c r="C11" t="n">
         <v>18.875</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>12.94246482849121</v>
+        <v>12.94245719909668</v>
       </c>
       <c r="C12" t="n">
         <v>17.64500045776367</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.99013519287109</v>
+        <v>12.99013423919678</v>
       </c>
       <c r="C13" t="n">
         <v>17.70999908447266</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>12.81409549713135</v>
+        <v>12.8140983581543</v>
       </c>
       <c r="C14" t="n">
         <v>17.46999931335449</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>11.332444190979</v>
+        <v>11.33244800567627</v>
       </c>
       <c r="C15" t="n">
         <v>15.44999980926514</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.5011510848999</v>
+        <v>11.50114822387695</v>
       </c>
       <c r="C16" t="n">
         <v>15.68000030517578</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>10.56594657897949</v>
+        <v>10.56594848632812</v>
       </c>
       <c r="C18" t="n">
         <v>14.40499973297119</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>9.623412132263184</v>
+        <v>9.623411178588867</v>
       </c>
       <c r="C19" t="n">
         <v>13.11999988555908</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>9.784778594970703</v>
+        <v>9.784780502319336</v>
       </c>
       <c r="C20" t="n">
         <v>13.34000015258789</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>10.10385036468506</v>
+        <v>10.10384559631348</v>
       </c>
       <c r="C21" t="n">
         <v>13.77499961853027</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>9.608738899230957</v>
+        <v>9.608745574951172</v>
       </c>
       <c r="C22" t="n">
         <v>13.10000038146973</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>9.784778594970703</v>
+        <v>9.784780502319336</v>
       </c>
       <c r="C23" t="n">
         <v>13.34000015258789</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>8.578184127807617</v>
+        <v>8.578186988830566</v>
       </c>
       <c r="C24" t="n">
         <v>11.69499969482422</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>7.507291793823242</v>
+        <v>7.507288455963135</v>
       </c>
       <c r="C25" t="n">
         <v>10.23499965667725</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>6.935163021087646</v>
+        <v>6.935161590576172</v>
       </c>
       <c r="C26" t="n">
         <v>9.454999923706055</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>6.594089984893799</v>
+        <v>6.594088554382324</v>
       </c>
       <c r="C27" t="n">
         <v>8.989999771118164</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>6.418054103851318</v>
+        <v>6.418051719665527</v>
       </c>
       <c r="C28" t="n">
         <v>8.75</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>5.952283382415771</v>
+        <v>5.952284336090088</v>
       </c>
       <c r="C29" t="n">
         <v>8.114999771118164</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>6.671105861663818</v>
+        <v>6.671108722686768</v>
       </c>
       <c r="C30" t="n">
         <v>9.095000267028809</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.772578239440918</v>
+        <v>5.772580146789551</v>
       </c>
       <c r="C31" t="n">
         <v>7.869999885559082</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>5.387495517730713</v>
+        <v>5.387496471405029</v>
       </c>
       <c r="C32" t="n">
         <v>7.34499979019165</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>5.453511238098145</v>
+        <v>5.453510284423828</v>
       </c>
       <c r="C34" t="n">
         <v>7.434999942779541</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>4.81537389755249</v>
+        <v>4.815371513366699</v>
       </c>
       <c r="C35" t="n">
         <v>6.565000057220459</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>3.275040149688721</v>
+        <v>3.275041818618774</v>
       </c>
       <c r="C36" t="n">
         <v>4.465000152587891</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>3.469416618347168</v>
+        <v>3.469415903091431</v>
       </c>
       <c r="C37" t="n">
         <v>4.730000019073486</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>3.462080001831055</v>
+        <v>3.462081670761108</v>
       </c>
       <c r="C38" t="n">
         <v>4.71999979019165</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>3.355725288391113</v>
+        <v>3.355724811553955</v>
       </c>
       <c r="C39" t="n">
         <v>4.574999809265137</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>4.074544906616211</v>
+        <v>4.074546813964844</v>
       </c>
       <c r="C40" t="n">
         <v>5.554999828338623</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>5.094100475311279</v>
+        <v>5.094099044799805</v>
       </c>
       <c r="C43" t="n">
         <v>6.945000171661377</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>6.491402149200439</v>
+        <v>6.491401672363281</v>
       </c>
       <c r="C44" t="n">
         <v>8.850000381469727</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>6.964502334594727</v>
+        <v>6.964500904083252</v>
       </c>
       <c r="C45" t="n">
         <v>9.494999885559082</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>7.573300838470459</v>
+        <v>7.573300361633301</v>
       </c>
       <c r="C46" t="n">
         <v>10.32499980926514</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>8.031733512878418</v>
+        <v>8.031731605529785</v>
       </c>
       <c r="C48" t="n">
         <v>10.94999980926514</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>8.457161903381348</v>
+        <v>8.457160949707031</v>
       </c>
       <c r="C49" t="n">
         <v>11.52999973297119</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.991390705108643</v>
+        <v>7.991395473480225</v>
       </c>
       <c r="C50" t="n">
         <v>10.89500045776367</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>8.402145385742188</v>
+        <v>8.40214729309082</v>
       </c>
       <c r="C51" t="n">
         <v>11.45499992370605</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>8.900922775268555</v>
+        <v>8.900918006896973</v>
       </c>
       <c r="C52" t="n">
         <v>12.13500022888184</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>9.567525863647461</v>
+        <v>9.567524909973145</v>
       </c>
       <c r="C53" t="n">
         <v>12.98999977111816</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>9.534385681152344</v>
+        <v>9.534380912780762</v>
       </c>
       <c r="C54" t="n">
         <v>12.94499969482422</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>8.948843002319336</v>
+        <v>8.94883918762207</v>
       </c>
       <c r="C55" t="n">
         <v>12.14999961853027</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>9.151388168334961</v>
+        <v>9.151387214660645</v>
       </c>
       <c r="C56" t="n">
         <v>12.42500019073486</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.507235527038574</v>
+        <v>8.507234573364258</v>
       </c>
       <c r="C57" t="n">
         <v>11.48999977111816</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>9.45865535736084</v>
+        <v>9.458651542663574</v>
       </c>
       <c r="C58" t="n">
         <v>12.77499961853027</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>10.57296085357666</v>
+        <v>10.57296562194824</v>
       </c>
       <c r="C59" t="n">
         <v>14.27999973297119</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>11.3762035369873</v>
+        <v>11.37620735168457</v>
       </c>
       <c r="C60" t="n">
         <v>15.30000019073486</v>
@@ -1748,7 +1748,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>11.72195243835449</v>
+        <v>11.72195148468018</v>
       </c>
       <c r="C62" t="n">
         <v>15.76500034332275</v>
@@ -1777,7 +1777,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.31014156341553</v>
+        <v>12.31014060974121</v>
       </c>
       <c r="C63" t="n">
         <v>16.48999977111816</v>
@@ -1806,7 +1806,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>13.79198551177979</v>
+        <v>13.79198741912842</v>
       </c>
       <c r="C64" t="n">
         <v>18.47500038146973</v>
@@ -1835,7 +1835,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.51204013824463</v>
+        <v>13.51204204559326</v>
       </c>
       <c r="C65" t="n">
         <v>18.10000038146973</v>
@@ -1864,7 +1864,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.78130626678467</v>
+        <v>13.78131103515625</v>
       </c>
       <c r="C66" t="n">
         <v>18.39500045776367</v>
@@ -1893,7 +1893,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>14.79271221160889</v>
+        <v>14.79271697998047</v>
       </c>
       <c r="C67" t="n">
         <v>19.7450008392334</v>
@@ -1922,7 +1922,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>15.01746368408203</v>
+        <v>15.01747035980225</v>
       </c>
       <c r="C68" t="n">
         <v>20.04500007629395</v>
@@ -1951,7 +1951,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>14.51821231842041</v>
+        <v>14.51821327209473</v>
       </c>
       <c r="C69" t="n">
         <v>19.30999946594238</v>
@@ -1980,7 +1980,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>14.0182409286499</v>
+        <v>14.01822853088379</v>
       </c>
       <c r="C70" t="n">
         <v>18.64500045776367</v>
@@ -2009,7 +2009,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>15.92417812347412</v>
+        <v>15.92416763305664</v>
       </c>
       <c r="C71" t="n">
         <v>21.18000030517578</v>
@@ -2067,7 +2067,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>17.36393356323242</v>
+        <v>17.36394691467285</v>
       </c>
       <c r="C73" t="n">
         <v>23.0049991607666</v>
@@ -2125,7 +2125,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>18.39099502563477</v>
+        <v>18.39100074768066</v>
       </c>
       <c r="C75" t="n">
         <v>24.28000068664551</v>
@@ -2154,7 +2154,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>21.16706848144531</v>
+        <v>21.16707038879395</v>
       </c>
       <c r="C76" t="n">
         <v>27.94499969482422</v>
@@ -2183,7 +2183,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>21.72758483886719</v>
+        <v>21.72759056091309</v>
       </c>
       <c r="C77" t="n">
         <v>28.68499946594238</v>
@@ -2212,7 +2212,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>20.85214996337891</v>
+        <v>20.85215187072754</v>
       </c>
       <c r="C78" t="n">
         <v>27.44499969482422</v>
@@ -2270,7 +2270,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>17.20140266418457</v>
+        <v>17.20141220092773</v>
       </c>
       <c r="C80" t="n">
         <v>22.63999938964844</v>
@@ -2299,7 +2299,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>18.91957855224609</v>
+        <v>18.91957473754883</v>
       </c>
       <c r="C81" t="n">
         <v>24.80500030517578</v>
@@ -2357,7 +2357,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.50470733642578</v>
+        <v>17.50470924377441</v>
       </c>
       <c r="C83" t="n">
         <v>22.95000076293945</v>
@@ -2386,7 +2386,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>19.86376571655273</v>
+        <v>19.86377716064453</v>
       </c>
       <c r="C84" t="n">
         <v>25.93499946594238</v>
@@ -2415,7 +2415,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>20.53776931762695</v>
+        <v>20.53777122497559</v>
       </c>
       <c r="C85" t="n">
         <v>26.81500053405762</v>
@@ -2444,7 +2444,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>21.49131965637207</v>
+        <v>21.49132537841797</v>
       </c>
       <c r="C86" t="n">
         <v>28.05999946594238</v>
@@ -2473,7 +2473,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>21.08391380310059</v>
+        <v>21.08390998840332</v>
       </c>
       <c r="C87" t="n">
         <v>27.42499923706055</v>
@@ -2502,7 +2502,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>21.89112854003906</v>
+        <v>21.89113807678223</v>
       </c>
       <c r="C88" t="n">
         <v>28.47500038146973</v>
@@ -2531,7 +2531,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>23.38642501831055</v>
+        <v>23.38642311096191</v>
       </c>
       <c r="C89" t="n">
         <v>30.42000007629395</v>
@@ -2560,7 +2560,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>24.35237312316895</v>
+        <v>24.35237503051758</v>
       </c>
       <c r="C90" t="n">
         <v>31.56999969482422</v>
@@ -2589,7 +2589,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.26645660400391</v>
+        <v>25.26645088195801</v>
       </c>
       <c r="C91" t="n">
         <v>32.75500106811523</v>
@@ -2618,7 +2618,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>27.49574089050293</v>
+        <v>27.49573516845703</v>
       </c>
       <c r="C92" t="n">
         <v>35.64500045776367</v>
@@ -2647,7 +2647,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>27.27618980407715</v>
+        <v>27.27619552612305</v>
       </c>
       <c r="C93" t="n">
         <v>35.2599983215332</v>
@@ -2676,7 +2676,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>29.77096366882324</v>
+        <v>29.77095985412598</v>
       </c>
       <c r="C94" t="n">
         <v>38.48500061035156</v>
@@ -2705,7 +2705,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>31.34906005859375</v>
+        <v>31.34904289245605</v>
       </c>
       <c r="C95" t="n">
         <v>40.52500152587891</v>
@@ -2734,7 +2734,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>31.60910797119141</v>
+        <v>31.60911178588867</v>
       </c>
       <c r="C96" t="n">
         <v>40.72999954223633</v>
@@ -2763,7 +2763,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>30.4178466796875</v>
+        <v>30.4178524017334</v>
       </c>
       <c r="C97" t="n">
         <v>39.19499969482422</v>
@@ -2792,7 +2792,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>27.59684944152832</v>
+        <v>27.59685516357422</v>
       </c>
       <c r="C98" t="n">
         <v>35.56000137329102</v>
@@ -2821,7 +2821,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>27.63895988464355</v>
+        <v>27.63897132873535</v>
       </c>
       <c r="C99" t="n">
         <v>35.47999954223633</v>
@@ -2850,7 +2850,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>28.5815486907959</v>
+        <v>28.58155632019043</v>
       </c>
       <c r="C100" t="n">
         <v>36.68999862670898</v>
@@ -2879,7 +2879,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>27.50653266906738</v>
+        <v>27.50653839111328</v>
       </c>
       <c r="C101" t="n">
         <v>35.31000137329102</v>
@@ -2908,7 +2908,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>28.63199043273926</v>
+        <v>28.63199234008789</v>
       </c>
       <c r="C102" t="n">
         <v>36.61999893188477</v>
@@ -2937,7 +2937,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>30.25045204162598</v>
+        <v>30.25045013427734</v>
       </c>
       <c r="C103" t="n">
         <v>38.68999862670898</v>
@@ -2966,7 +2966,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>30.36772537231445</v>
+        <v>30.36773300170898</v>
       </c>
       <c r="C104" t="n">
         <v>38.84000015258789</v>
@@ -2995,7 +2995,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>30.52090263366699</v>
+        <v>30.52091217041016</v>
       </c>
       <c r="C105" t="n">
         <v>38.90499877929688</v>
@@ -3024,7 +3024,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>29.59913444519043</v>
+        <v>29.59912109375</v>
       </c>
       <c r="C106" t="n">
         <v>37.72999954223633</v>
@@ -3053,7 +3053,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>29.63834381103516</v>
+        <v>29.63834190368652</v>
       </c>
       <c r="C107" t="n">
         <v>37.77999877929688</v>
@@ -3082,7 +3082,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>31.98614120483398</v>
+        <v>31.98614692687988</v>
       </c>
       <c r="C108" t="n">
         <v>40.60499954223633</v>
@@ -3111,7 +3111,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>32.31697845458984</v>
+        <v>32.31697463989258</v>
       </c>
       <c r="C109" t="n">
         <v>41.02500152587891</v>
@@ -3140,7 +3140,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>34.47538375854492</v>
+        <v>34.47539138793945</v>
       </c>
       <c r="C110" t="n">
         <v>43.76499938964844</v>
@@ -3169,7 +3169,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>36.95725631713867</v>
+        <v>36.95726013183594</v>
       </c>
       <c r="C111" t="n">
         <v>46.74499893188477</v>
@@ -3198,7 +3198,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>37.43558120727539</v>
+        <v>37.43557739257812</v>
       </c>
       <c r="C112" t="n">
         <v>47.34999847412109</v>
@@ -3227,7 +3227,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>39.19865798950195</v>
+        <v>39.19864654541016</v>
       </c>
       <c r="C113" t="n">
         <v>49.58000183105469</v>
@@ -3256,7 +3256,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>41.21101379394531</v>
+        <v>41.21100234985352</v>
       </c>
       <c r="C114" t="n">
         <v>51.95999908447266</v>
@@ -3285,7 +3285,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>42.52760696411133</v>
+        <v>42.52761077880859</v>
       </c>
       <c r="C115" t="n">
         <v>53.61999893188477</v>
@@ -3343,7 +3343,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>43.51175308227539</v>
+        <v>43.51175689697266</v>
       </c>
       <c r="C117" t="n">
         <v>54.70999908447266</v>
@@ -3372,7 +3372,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>45.20578765869141</v>
+        <v>45.20578002929688</v>
       </c>
       <c r="C118" t="n">
         <v>56.84000015258789</v>
@@ -3401,7 +3401,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>49.76294326782227</v>
+        <v>49.762939453125</v>
       </c>
       <c r="C119" t="n">
         <v>62.56999969482422</v>
@@ -3488,7 +3488,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>48.48785400390625</v>
+        <v>48.48786163330078</v>
       </c>
       <c r="C122" t="n">
         <v>60.77000045776367</v>
@@ -3517,7 +3517,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>46.59704208374023</v>
+        <v>46.5970344543457</v>
       </c>
       <c r="C123" t="n">
         <v>58.20999908447266</v>
@@ -3546,7 +3546,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>47.7897834777832</v>
+        <v>47.78977966308594</v>
       </c>
       <c r="C124" t="n">
         <v>59.70000076293945</v>
@@ -3575,7 +3575,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>45.01205825805664</v>
+        <v>45.01206588745117</v>
       </c>
       <c r="C125" t="n">
         <v>56.22999954223633</v>
@@ -3604,7 +3604,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>44.0931282043457</v>
+        <v>44.09312438964844</v>
       </c>
       <c r="C126" t="n">
         <v>54.88999938964844</v>
@@ -3633,7 +3633,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>45.88448333740234</v>
+        <v>45.88447189331055</v>
       </c>
       <c r="C127" t="n">
         <v>57.11999893188477</v>
@@ -3691,7 +3691,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>45.32684707641602</v>
+        <v>45.32686614990234</v>
       </c>
       <c r="C129" t="n">
         <v>56.22999954223633</v>
@@ -3749,7 +3749,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>42.77957534790039</v>
+        <v>42.77957916259766</v>
       </c>
       <c r="C131" t="n">
         <v>53.06999969482422</v>
@@ -3865,7 +3865,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>46.26263427734375</v>
+        <v>46.26264190673828</v>
       </c>
       <c r="C135" t="n">
         <v>56.86999893188477</v>
@@ -3894,7 +3894,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>47.49912643432617</v>
+        <v>47.49911499023438</v>
       </c>
       <c r="C136" t="n">
         <v>58.38999938964844</v>
@@ -3923,7 +3923,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>48.85763931274414</v>
+        <v>48.85763549804688</v>
       </c>
       <c r="C137" t="n">
         <v>60.06000137329102</v>
@@ -3952,7 +3952,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>51.95864868164062</v>
+        <v>51.95864105224609</v>
       </c>
       <c r="C138" t="n">
         <v>63.61000061035156</v>
@@ -3981,7 +3981,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>47.62943649291992</v>
+        <v>47.62944412231445</v>
       </c>
       <c r="C139" t="n">
         <v>58.31000137329102</v>
@@ -4010,7 +4010,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>44.09257125854492</v>
+        <v>44.09256362915039</v>
       </c>
       <c r="C140" t="n">
         <v>53.97999954223633</v>
@@ -4039,7 +4039,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>45.0136604309082</v>
+        <v>45.013671875</v>
       </c>
       <c r="C141" t="n">
         <v>54.86000061035156</v>
@@ -4068,7 +4068,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>44.07007217407227</v>
+        <v>44.070068359375</v>
       </c>
       <c r="C142" t="n">
         <v>53.70999908447266</v>
@@ -4097,7 +4097,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>44.99724578857422</v>
+        <v>44.99725723266602</v>
       </c>
       <c r="C143" t="n">
         <v>54.84000015258789</v>
@@ -4155,7 +4155,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>47.37202835083008</v>
+        <v>47.37203598022461</v>
       </c>
       <c r="C145" t="n">
         <v>57.43000030517578</v>
@@ -4184,7 +4184,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>46.86061859130859</v>
+        <v>46.86061477661133</v>
       </c>
       <c r="C146" t="n">
         <v>56.81000137329102</v>
@@ -4213,7 +4213,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>47.35529708862305</v>
+        <v>47.35528182983398</v>
       </c>
       <c r="C147" t="n">
         <v>57.09999847412109</v>
@@ -4242,7 +4242,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>48.01047897338867</v>
+        <v>48.01047134399414</v>
       </c>
       <c r="C148" t="n">
         <v>57.88999938964844</v>
@@ -4271,7 +4271,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>47.74508666992188</v>
+        <v>47.74508285522461</v>
       </c>
       <c r="C149" t="n">
         <v>57.56999969482422</v>
@@ -4300,7 +4300,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>47.24443817138672</v>
+        <v>47.24444580078125</v>
       </c>
       <c r="C150" t="n">
         <v>56.66999816894531</v>
@@ -4358,7 +4358,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>43.67631912231445</v>
+        <v>43.67631149291992</v>
       </c>
       <c r="C152" t="n">
         <v>52.38999938964844</v>
@@ -4387,7 +4387,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>44.87023162841797</v>
+        <v>44.87023544311523</v>
       </c>
       <c r="C153" t="n">
         <v>53.45000076293945</v>
@@ -4416,7 +4416,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>47.716064453125</v>
+        <v>47.7160758972168</v>
       </c>
       <c r="C154" t="n">
         <v>56.84000015258789</v>
@@ -4445,7 +4445,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>48.91653442382812</v>
+        <v>48.91652679443359</v>
       </c>
       <c r="C155" t="n">
         <v>58.27000045776367</v>
@@ -4474,7 +4474,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>56.31085586547852</v>
+        <v>56.31086730957031</v>
       </c>
       <c r="C156" t="n">
         <v>66.72000122070312</v>
@@ -4503,7 +4503,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>54.35280990600586</v>
+        <v>54.35280609130859</v>
       </c>
       <c r="C157" t="n">
         <v>64.40000152587891</v>
@@ -4532,7 +4532,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>57.50932312011719</v>
+        <v>57.50933074951172</v>
       </c>
       <c r="C158" t="n">
         <v>68.13999938964844</v>
@@ -4561,7 +4561,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>59.60806274414062</v>
+        <v>59.60804748535156</v>
       </c>
       <c r="C159" t="n">
         <v>70.26000213623047</v>
@@ -4590,7 +4590,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>63.06948852539062</v>
+        <v>63.06948471069336</v>
       </c>
       <c r="C160" t="n">
         <v>74.33999633789062</v>
@@ -4619,7 +4619,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>65.90312194824219</v>
+        <v>65.90310668945312</v>
       </c>
       <c r="C161" t="n">
         <v>77.68000030517578</v>
@@ -4648,7 +4648,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>64.82807922363281</v>
+        <v>64.82807159423828</v>
       </c>
       <c r="C162" t="n">
         <v>76.05999755859375</v>
@@ -4706,7 +4706,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>80.70695495605469</v>
+        <v>80.70694732666016</v>
       </c>
       <c r="C164" t="n">
         <v>94.69000244140625</v>
@@ -4735,7 +4735,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>82.61275482177734</v>
+        <v>82.61274719238281</v>
       </c>
       <c r="C165" t="n">
         <v>96.55999755859375</v>
@@ -4764,7 +4764,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>75.64850616455078</v>
+        <v>75.64849853515625</v>
       </c>
       <c r="C166" t="n">
         <v>88.41999816894531</v>
@@ -4793,7 +4793,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>72.34605407714844</v>
+        <v>72.34603881835938</v>
       </c>
       <c r="C167" t="n">
         <v>84.55999755859375</v>
@@ -4851,7 +4851,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>75.59671783447266</v>
+        <v>75.59672546386719</v>
       </c>
       <c r="C169" t="n">
         <v>87.91999816894531</v>
@@ -4880,7 +4880,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>72.93985748291016</v>
+        <v>72.93982696533203</v>
       </c>
       <c r="C170" t="n">
         <v>84.83000183105469</v>
@@ -4938,7 +4938,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>56.78902816772461</v>
+        <v>56.78902053833008</v>
       </c>
       <c r="C172" t="n">
         <v>65.73999786376953</v>
@@ -4967,7 +4967,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>66.28265380859375</v>
+        <v>66.28266906738281</v>
       </c>
       <c r="C173" t="n">
         <v>76.73000335693359</v>
@@ -4996,7 +4996,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>67.75182342529297</v>
+        <v>67.75184631347656</v>
       </c>
       <c r="C174" t="n">
         <v>77.98999786376953</v>
@@ -5025,7 +5025,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>63.9294548034668</v>
+        <v>63.9294319152832</v>
       </c>
       <c r="C175" t="n">
         <v>73.58999633789062</v>
@@ -5054,7 +5054,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>66.48350524902344</v>
+        <v>66.48348236083984</v>
       </c>
       <c r="C176" t="n">
         <v>76.52999877929688</v>
@@ -5083,7 +5083,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>73.78034973144531</v>
+        <v>73.78036499023438</v>
       </c>
       <c r="C177" t="n">
         <v>84.47000122070312</v>
@@ -5141,7 +5141,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>75.95524597167969</v>
+        <v>75.95526123046875</v>
       </c>
       <c r="C179" t="n">
         <v>86.95999908447266</v>
@@ -5170,7 +5170,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>86.01931762695312</v>
+        <v>86.01932525634766</v>
       </c>
       <c r="C180" t="n">
         <v>98.01999664306641</v>
@@ -5199,7 +5199,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>93.88236236572266</v>
+        <v>93.88233184814453</v>
       </c>
       <c r="C181" t="n">
         <v>106.9800033569336</v>
@@ -5228,7 +5228,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>84.95746612548828</v>
+        <v>84.95747375488281</v>
       </c>
       <c r="C182" t="n">
         <v>96.80999755859375</v>
@@ -5257,7 +5257,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>95.20742034912109</v>
+        <v>95.2073974609375</v>
       </c>
       <c r="C183" t="n">
         <v>108.0299987792969</v>
@@ -5286,7 +5286,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>96.30022430419922</v>
+        <v>96.30023956298828</v>
       </c>
       <c r="C184" t="n">
         <v>109.2699966430664</v>
@@ -5315,7 +5315,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>100.900634765625</v>
+        <v>100.9006500244141</v>
       </c>
       <c r="C185" t="n">
         <v>114.4899978637695</v>
@@ -5344,7 +5344,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>100.7623596191406</v>
+        <v>100.7623748779297</v>
       </c>
       <c r="C186" t="n">
         <v>113.879997253418</v>
@@ -5402,7 +5402,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>107.4427032470703</v>
+        <v>107.4426879882812</v>
       </c>
       <c r="C188" t="n">
         <v>121.4300003051758</v>
@@ -5460,7 +5460,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>97.982421875</v>
+        <v>97.98241424560547</v>
       </c>
       <c r="C190" t="n">
         <v>110.3099975585938</v>
@@ -5489,7 +5489,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>94.21624755859375</v>
+        <v>94.21625518798828</v>
       </c>
       <c r="C191" t="n">
         <v>106.0699996948242</v>
@@ -5518,7 +5518,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>97.80721282958984</v>
+        <v>97.80719757080078</v>
       </c>
       <c r="C192" t="n">
         <v>109.6399993896484</v>
@@ -5605,7 +5605,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>82.29883575439453</v>
+        <v>82.298828125</v>
       </c>
       <c r="C195" t="n">
         <v>91.79000091552734</v>
@@ -5692,7 +5692,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>70.87875366210938</v>
+        <v>70.87876892089844</v>
       </c>
       <c r="C198" t="n">
         <v>78.5</v>
@@ -5721,7 +5721,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>68.97361755371094</v>
+        <v>68.97360992431641</v>
       </c>
       <c r="C199" t="n">
         <v>76.38999938964844</v>
@@ -5808,7 +5808,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>76.51300811767578</v>
+        <v>76.51303100585938</v>
       </c>
       <c r="C202" t="n">
         <v>84.26000213623047</v>
@@ -5837,7 +5837,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>78.62880706787109</v>
+        <v>78.62879180908203</v>
       </c>
       <c r="C203" t="n">
         <v>86.58999633789062</v>
@@ -5866,7 +5866,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>93.33694458007812</v>
+        <v>93.33695220947266</v>
       </c>
       <c r="C204" t="n">
         <v>102.1999969482422</v>
@@ -5895,7 +5895,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>90.59709930419922</v>
+        <v>90.59711456298828</v>
       </c>
       <c r="C205" t="n">
         <v>99.19999694824219</v>
@@ -5924,7 +5924,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>99.67507171630859</v>
+        <v>99.67508697509766</v>
       </c>
       <c r="C206" t="n">
         <v>109.1399993896484</v>
@@ -6011,7 +6011,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>104.901496887207</v>
+        <v>104.9014892578125</v>
       </c>
       <c r="C209" t="n">
         <v>114.2900009155273</v>
@@ -6127,7 +6127,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>90.36026763916016</v>
+        <v>90.36028289794922</v>
       </c>
       <c r="C213" t="n">
         <v>97.44000244140625</v>
@@ -6156,7 +6156,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>84.63857269287109</v>
+        <v>84.63855743408203</v>
       </c>
       <c r="C214" t="n">
         <v>91.26999664306641</v>
@@ -6214,7 +6214,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>92.59115600585938</v>
+        <v>92.59114837646484</v>
       </c>
       <c r="C216" t="n">
         <v>99.30000305175781</v>
@@ -6243,7 +6243,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>89.52342987060547</v>
+        <v>89.52342224121094</v>
       </c>
       <c r="C217" t="n">
         <v>96.01000213623047</v>
@@ -6272,7 +6272,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>86.74476623535156</v>
+        <v>86.74475860595703</v>
       </c>
       <c r="C218" t="n">
         <v>93.02999877929688</v>
@@ -6330,7 +6330,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>85.72826385498047</v>
+        <v>85.72824859619141</v>
       </c>
       <c r="C220" t="n">
         <v>91.38999938964844</v>
@@ -6359,7 +6359,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>83.00791168212891</v>
+        <v>83.00791931152344</v>
       </c>
       <c r="C221" t="n">
         <v>88.48999786376953</v>
@@ -6417,7 +6417,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>73.58113098144531</v>
+        <v>73.58112335205078</v>
       </c>
       <c r="C223" t="n">
         <v>77.84999847412109</v>
@@ -6446,7 +6446,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>73.67564392089844</v>
+        <v>73.67562866210938</v>
       </c>
       <c r="C224" t="n">
         <v>77.94999694824219</v>
@@ -6475,7 +6475,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>89.92452239990234</v>
+        <v>89.92453002929688</v>
       </c>
       <c r="C225" t="n">
         <v>94.56999969482422</v>
@@ -6504,7 +6504,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>92.70108795166016</v>
+        <v>92.70108032226562</v>
       </c>
       <c r="C226" t="n">
         <v>97.48999786376953</v>
@@ -6533,7 +6533,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>92.90077209472656</v>
+        <v>92.90076446533203</v>
       </c>
       <c r="C227" t="n">
         <v>97.69999694824219</v>
@@ -6562,7 +6562,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>98.02957916259766</v>
+        <v>98.02956390380859</v>
       </c>
       <c r="C228" t="n">
         <v>102.4599990844727</v>
@@ -6620,7 +6620,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>103.0238647460938</v>
+        <v>103.0238571166992</v>
       </c>
       <c r="C230" t="n">
         <v>107.6800003051758</v>
@@ -6707,7 +6707,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>77.00428009033203</v>
+        <v>77.00428771972656</v>
       </c>
       <c r="C233" t="n">
         <v>80.05000305175781</v>
@@ -6736,7 +6736,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>81.32440185546875</v>
+        <v>81.32439422607422</v>
       </c>
       <c r="C234" t="n">
         <v>83.94999694824219</v>
@@ -6765,7 +6765,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>88.76419830322266</v>
+        <v>88.76420593261719</v>
       </c>
       <c r="C235" t="n">
         <v>91.62999725341797</v>
@@ -6794,7 +6794,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>86.3714599609375</v>
+        <v>86.37145233154297</v>
       </c>
       <c r="C236" t="n">
         <v>89.16000366210938</v>
@@ -6852,7 +6852,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>82.49481201171875</v>
+        <v>82.49480438232422</v>
       </c>
       <c r="C238" t="n">
         <v>84.59999847412109</v>
@@ -6881,7 +6881,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>78.85763549804688</v>
+        <v>78.85762786865234</v>
       </c>
       <c r="C239" t="n">
         <v>80.87000274658203</v>
@@ -6968,7 +6968,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>90.30966186523438</v>
+        <v>90.30966949462891</v>
       </c>
       <c r="C242" t="n">
         <v>91.94999694824219</v>
@@ -6997,7 +6997,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>96.89222717285156</v>
+        <v>96.89223480224609</v>
       </c>
       <c r="C243" t="n">
         <v>98.01999664306641</v>
